--- a/Faculties/Natural Science/Experimental/Programmes Natural Science.xlsx
+++ b/Faculties/Natural Science/Experimental/Programmes Natural Science.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\Experimental\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94ED27CA-EDE0-4632-A4A2-85DE96DA9024}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545FD419-F49B-4A34-BC3D-6C0C92D19B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12780" yWindow="2760" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,121 +180,121 @@
     <t>Doctor of Philosophy</t>
   </si>
   <si>
-    <t>Duration  Years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Applied Geology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Biodiversity and Conservation Biology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Biotechnology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Chemical Sciences </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Computer Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Environment and Water Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Mathematics and Statistical Sciences </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Medical Bioscience </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc  Physical Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Applied Geology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Astrophysics </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Biodiversity and Conservation Biology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Biotechnology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Chemistry </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Computational Finance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Computer Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Environment and Water Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Mathematics </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Medical Bioscience </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Physical Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Population Studies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BScHons  Statistical Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPhil  Population Studies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Applied Geology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Biodiversity and Conservation Biology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Bioinformatics </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Biotechnology </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Chemical Sciences </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Computational Finance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Computer Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Environment and Water Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Mathematical Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Medical Bioscience </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Nanoscience </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Pharmaceutical Sciences </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Pharmacy Administration and Policy Regulation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Physical Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc  Statistical Science </t>
+    <t>Duration  Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Environment and Water Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Medical Bioscience </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Physical Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Applied Geology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Astrophysics </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Biodiversity and Conservation Biology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Biotechnology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Chemistry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Computational Finance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Computer Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Environment and Water Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Mathematics </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Medical Bioscience </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Physical Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Population Studies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BScHons Statistical Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPhil Population Studies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Applied Geology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Biodiversity and Conservation Biology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Bioinformatics </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Biotechnology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Chemical Sciences </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Computational Finance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Computer Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Environment and Water Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Mathematical Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Medical Bioscience </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Nanoscience </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Pharmaceutical Sciences </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Pharmacy Administration and Policy Regulation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Physical Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Statistical Science </t>
   </si>
 </sst>
 </file>
@@ -366,10 +366,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1022,7 +1018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="78" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>34</v>
       </c>
